--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0163.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0163.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Này, cậu, "Cộng Hưởng Giả mạnh nhất" của nhóm lính đánh thuê kia, sao lại đứng về phe chúng nó? Cậu thực sự phản bội ta à?!</t>
+          <t>Này, cậu, "Resonator mạnh nhất" của nhóm lính đánh thuê kia, sao lại đứng về phe chúng nó? Cậu thực sự phản bội tao à?!</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Còn cậu, Carty! Không phải tụi mình đã hứa sẽ cùng nhau làm nên chuyện lớn à?!</t>
+          <t>Còn mày, Carty! Không phải tụi mình đã hứa sẽ cùng nhau làm nên chuyện lớn à?!</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Cartethyia, cô hãy nhìn sang ta, {PlayerName}, và ông "Cộng Hưởng Giả Mạnh Nhất" đằng kia đi. Cô có nhận ra nụ cười của chúng ta không?</t>
+          <t>Cartethyia, cô hãy nhìn sang ta, {PlayerName}, và ông "Resonator Mạnh Nhất" đằng kia đi. Cô có nhận ra nụ cười của chúng ta không?</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Này, ngừng đánh ta đi! Đâu phải ý của ngươi à?</t>
+          <t>Này, ngừng đánh tao đi! Đâu phải ý của mày à?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Thật là để {PlayerName} có thể tỏ ra bá đạo khi {Male=anh;Female=chị} mở rương vậy!</t>
+          <t>Thật là để {PlayerName} có thể tỏ ra bá đạo khi {Male=he;Female=she} mở rương vậy!</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Vậy cô ấy là Đặc Nhiệm Số 3... Ta hiểu rồi. Chắc hẳn cô ấy là Cộng Hưởng Giả của Sentinel ở khu vực này phải không?</t>
+          <t>Vậy cô ấy là Đặc Nhiệm Số 3... Ta hiểu rồi. Chắc hẳn cô ấy là Resonator của Sentinel ở khu vực này phải không?</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Chỉ cần có {Male=anh ấy;Female=cô ấy} thật, ta mới là Camellya thật sự.</t>
+          <t>Chỉ cần có {Male=him;Female=her} thật, ta mới là Camellya thật sự.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vui trong vô nghĩa ư...? Thật ra ta chưa bao giờ thấy {PlayerName} như thế này cả...</t>
+          <t>Vui trong vô nghĩa ư...? Thật ra tao chưa bao giờ thấy {PlayerName} như thế này cả...</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Sao? Cuối cùng cũng sẵn sàng vứt bỏ cái &lt;ano=Tethys Hệ thống&gt;cỗ máy ngu ngốc&lt;/ano&gt; đó và gia nhập chúng ta ở New Black Shores chưa?</t>
+          <t>Sao? Cuối cùng cũng sẵn sàng vứt bỏ cái &lt;ano=Tethys System&gt;cỗ máy ngu ngốc&lt;/ano&gt; đó và gia nhập chúng ta ở New Black Shores chưa?</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Dù ta rất muốn tiếp tục trò chơi này thêm trăm năm, nghìn năm, thậm chí triệu năm nữa... Được rồi, được rồi, tạm dừng thôi. Nhưng chỉ là tạm thời thôi nhé.</t>
+          <t>Dù tao rất muốn tiếp tục trò chơi này thêm trăm năm, nghìn năm, thậm chí triệu năm nữa... Được rồi, được rồi, tạm dừng thôi. Nhưng chỉ là tạm thời thôi nhé.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Sao các người có thể làm vậy với ta? Đồ bắt nạt! Đợi đấy, ta sẽ trả thù cho mà xem!</t>
+          <t>Sao các người có thể làm vậy với tao? Đồ bắt nạt! Đợi đấy, tao sẽ trả thù cho mà xem!</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Dù sao thì theo luật lệ, trò chơi sẽ kết thúc khi {Male=hắn;Female=cô ta} bị bắt.</t>
+          <t>Dù sao thì theo luật lệ, trò chơi sẽ kết thúc khi {Male=he;Female=she} bị bắt.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Tadaa! Chào mừng đến với thế giới &lt;te href=800003&gt;Second Coming of Solaris&lt;/te&gt;!</t>
+          <t>Tadaa! Chào mừng đến với thế giới &lt;te href=800003&gt;Sự Trở Lại Của Solaris&lt;/te&gt;!</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Đợi đã, sao giờ ta lại thành một khối Lập Phương thế này?</t>
+          <t>Đợi đã, sao giờ tao lại thành một khối Lập Phương thế này?</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Chào Abbowser! Cậu giấu &lt;te href=800002&gt;Anniversary Cake&lt;/te&gt; ở đâu rồi?</t>
+          <t>Chào Abbowser! Cậu giấu &lt;te href=800002&gt;Bánh Kỷ Niệm&lt;/te&gt; ở đâu rồi?</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Đoán xem? Ta ăn nó rồi! Úi! Giờ cả thế giới này nằm trong tay ta rồi! Ha ha ha!</t>
+          <t>Đoán xem? Tao ăn nó rồi! Úi! Giờ cả thế giới này nằm trong tay tao rồi! Ha ha ha!</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Haha, phải công nhận, cậu mạnh thật đấy.</t>
+          <t>Haha, phải công nhận, mày mạnh thật đấy.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Nhưng cậu không phải đối thủ của thủ lĩnh chúng ta đâu, Cộng Hưởng Giả mạnh nhất trong nhóm lính đánh thuê của chúng ta!</t>
+          <t>Nhưng cậu không phải đối thủ của thủ lĩnh chúng ta đâu, Resonator mạnh nhất trong nhóm lính đánh thuê của chúng ta!</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>À, cậu đang nói về &lt;i&gt;cái&lt;/i&gt; &lt;te href=800004&gt;Cube&lt;/te&gt; ấy à... Haha, tôi nóng lòng muốn gặp lại hắn quá!</t>
+          <t>À, cậu đang nói về &lt;i&gt;cái&lt;/i&gt; &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; ấy à... Haha, tôi nóng lòng muốn gặp lại hắn quá!</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{PlayerName}, đến đúng lúc đấy! Sếp đã bị Elite Không. 3 bắt đi. Chúng ta cần cậu giúp giải cứu!</t>
+          <t>{PlayerName}, đến đúng lúc đấy! Sếp đã bị Elite No. 3 bắt đi. Chúng ta cần cậu giúp giải cứu!</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Đồ ngốc, cậu quên lời cuối của Sếp trước khi bị Elite Không.3 bắt đi rồi à?</t>
+          <t>Đồ ngốc, mày quên lời cuối của Sếp trước khi bị Elite No.3 bắt đi rồi à?</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, hãy nhớ rằng giờ tôi là thành viên ưu tú của một tổ chức tội ác đấy.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, hãy nhớ rằng giờ tôi là thành viên ưu tú của một tổ chức tội ác đấy.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Cẩu thả quá, {Male=anh;Female=chị} {PlayerName}. Sao lại để bị phục kích cùng một kiểu đến hai lần?</t>
+          <t>Cẩu thả quá, {Male=Mr.;Female=Ms.} {PlayerName}. Sao lại để bị phục kích cùng một kiểu đến hai lần?</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Ta là thiên tài đóng vai phản diện đấy!</t>
+          <t>Tao là thiên tài đóng vai phản diện đấy!</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Thôi, ta sẽ chơi nghiêm túc ở vòng sau đấy. Cậu chuẩn bị tinh thần đi nhé!</t>
+          <t>Thôi, tao sẽ chơi nghiêm túc ở vòng sau đấy. Cậu chuẩn bị tinh thần đi nhé!</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Kỹ năng đáng nể, {Male=thưa ngài;Female=thưa tiểu thư}.</t>
+          <t>Kỹ năng đáng nể, {Male=sir;Female=lady}.</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>{Male=Thưa ngài;Female=Thưa cô}, không mở rương ra xem sao? Tất cả đều do Quý bà Carlotta chuẩn bị riêng cho ngài đấy.</t>
+          <t>{Male=sir;Female=miss}, không mở rương ra xem sao? Tất cả đều do Quý bà Carlotta chuẩn bị riêng cho ngài đấy.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Anh em, bắt {Male=hắn;Female=cô ta} đi!</t>
+          <t>Anh em, bắt {Male=him;Female=her} đi!</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Pero? Cậu nhập làm một với Roccia rồi à?</t>
+          <t>Pero? Mày nhập làm một với Roccia rồi à?</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Roccia vừa ăn vụng một miếng &lt;te href=800002&gt;Anniversary Cake&lt;/te&gt; à?</t>
+          <t>Roccia vừa ăn vụng một miếng &lt;te href=800002&gt;Bánh Kỷ Niệm&lt;/te&gt; à?</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Ừ, họ là những người bạn quan trọng của ta.</t>
+          <t>Ừ, họ là những người bạn quan trọng của tao.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Gì? Cậu đã đoán ra rồi á? Tôi... ý tôi là, tôi đã biết thủ phạm từ lâu rồi! Đây là lãnh địa của tôi!</t>
+          <t>Gì? Mày đã đoán ra rồi á? Tôi... ý tôi là, tôi đã biết thủ phạm từ lâu rồi! Đây là lãnh địa của tôi!</t>
         </is>
       </c>
     </row>
